--- a/analises/vinhos/cotacao-18-garrafas-brancos-agosto-2026.xlsx
+++ b/analises/vinhos/cotacao-18-garrafas-brancos-agosto-2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
   <si>
     <t>Cotação — 18 garrafas do mesmo vinho · Pagamento via Pix</t>
   </si>
@@ -122,6 +122,18 @@
   </si>
   <si>
     <t>Uruguai</t>
+  </si>
+  <si>
+    <t>Marius By Michel Chapoutier Vermentino</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>Michel Chapoutier</t>
+  </si>
+  <si>
+    <t>França</t>
   </si>
 </sst>
 </file>
@@ -532,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -773,11 +785,31 @@
         <v>2160</v>
       </c>
     </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="4">
+        <v>100</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1800</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>